--- a/data/3FEB_25_26/clutch_data_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/clutch_data_25_26_3FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z889"/>
+  <dimension ref="A1:Z903"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80480,6 +80480,1266 @@
         <v>99.31999999999999</v>
       </c>
     </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C890" t="n">
+        <v>24</v>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="G890" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H890" t="n">
+        <v>162</v>
+      </c>
+      <c r="I890" t="n">
+        <v>0</v>
+      </c>
+      <c r="J890" t="n">
+        <v>1</v>
+      </c>
+      <c r="K890" t="n">
+        <v>0</v>
+      </c>
+      <c r="L890" t="n">
+        <v>1</v>
+      </c>
+      <c r="M890" t="n">
+        <v>0</v>
+      </c>
+      <c r="N890" t="n">
+        <v>0</v>
+      </c>
+      <c r="O890" t="n">
+        <v>0</v>
+      </c>
+      <c r="P890" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q890" t="n">
+        <v>0</v>
+      </c>
+      <c r="R890" t="n">
+        <v>0</v>
+      </c>
+      <c r="S890" t="n">
+        <v>0</v>
+      </c>
+      <c r="T890" t="n">
+        <v>0</v>
+      </c>
+      <c r="U890" t="n">
+        <v>1</v>
+      </c>
+      <c r="V890" t="n">
+        <v>0</v>
+      </c>
+      <c r="W890" t="n">
+        <v>1</v>
+      </c>
+      <c r="X890" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="Y890" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z890" t="n">
+        <v>-153.41</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C891" t="n">
+        <v>24</v>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>A. JIMENEZ FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="G891" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H891" t="n">
+        <v>132</v>
+      </c>
+      <c r="I891" t="n">
+        <v>0</v>
+      </c>
+      <c r="J891" t="n">
+        <v>0</v>
+      </c>
+      <c r="K891" t="n">
+        <v>0</v>
+      </c>
+      <c r="L891" t="n">
+        <v>0</v>
+      </c>
+      <c r="M891" t="n">
+        <v>0</v>
+      </c>
+      <c r="N891" t="n">
+        <v>0</v>
+      </c>
+      <c r="O891" t="n">
+        <v>0</v>
+      </c>
+      <c r="P891" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q891" t="n">
+        <v>0</v>
+      </c>
+      <c r="R891" t="n">
+        <v>0</v>
+      </c>
+      <c r="S891" t="n">
+        <v>1</v>
+      </c>
+      <c r="T891" t="n">
+        <v>0</v>
+      </c>
+      <c r="U891" t="n">
+        <v>2</v>
+      </c>
+      <c r="V891" t="n">
+        <v>1</v>
+      </c>
+      <c r="W891" t="n">
+        <v>1</v>
+      </c>
+      <c r="X891" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="Y891" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z891" t="n">
+        <v>-148.65</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C892" t="n">
+        <v>24</v>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>D. RODRIGUEZ GARCIA</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="G892" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H892" t="n">
+        <v>162</v>
+      </c>
+      <c r="I892" t="n">
+        <v>0</v>
+      </c>
+      <c r="J892" t="n">
+        <v>0</v>
+      </c>
+      <c r="K892" t="n">
+        <v>0</v>
+      </c>
+      <c r="L892" t="n">
+        <v>0</v>
+      </c>
+      <c r="M892" t="n">
+        <v>0</v>
+      </c>
+      <c r="N892" t="n">
+        <v>2</v>
+      </c>
+      <c r="O892" t="n">
+        <v>1</v>
+      </c>
+      <c r="P892" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q892" t="n">
+        <v>0</v>
+      </c>
+      <c r="R892" t="n">
+        <v>0</v>
+      </c>
+      <c r="S892" t="n">
+        <v>1</v>
+      </c>
+      <c r="T892" t="n">
+        <v>0</v>
+      </c>
+      <c r="U892" t="n">
+        <v>0</v>
+      </c>
+      <c r="V892" t="n">
+        <v>0</v>
+      </c>
+      <c r="W892" t="n">
+        <v>0</v>
+      </c>
+      <c r="X892" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="Y892" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z892" t="n">
+        <v>-153.41</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C893" t="n">
+        <v>24</v>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>M. NIANG</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="G893" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H893" t="n">
+        <v>69</v>
+      </c>
+      <c r="I893" t="n">
+        <v>0</v>
+      </c>
+      <c r="J893" t="n">
+        <v>0</v>
+      </c>
+      <c r="K893" t="n">
+        <v>0</v>
+      </c>
+      <c r="L893" t="n">
+        <v>0</v>
+      </c>
+      <c r="M893" t="n">
+        <v>0</v>
+      </c>
+      <c r="N893" t="n">
+        <v>0</v>
+      </c>
+      <c r="O893" t="n">
+        <v>0</v>
+      </c>
+      <c r="P893" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q893" t="n">
+        <v>0</v>
+      </c>
+      <c r="R893" t="n">
+        <v>0</v>
+      </c>
+      <c r="S893" t="n">
+        <v>0</v>
+      </c>
+      <c r="T893" t="n">
+        <v>0</v>
+      </c>
+      <c r="U893" t="n">
+        <v>0</v>
+      </c>
+      <c r="V893" t="n">
+        <v>0</v>
+      </c>
+      <c r="W893" t="n">
+        <v>0</v>
+      </c>
+      <c r="X893" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y893" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z893" t="n">
+        <v>-94.7</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C894" t="n">
+        <v>24</v>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>M. RODRÍGUEZ RIVEROL</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="G894" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H894" t="n">
+        <v>30</v>
+      </c>
+      <c r="I894" t="n">
+        <v>0</v>
+      </c>
+      <c r="J894" t="n">
+        <v>0</v>
+      </c>
+      <c r="K894" t="n">
+        <v>0</v>
+      </c>
+      <c r="L894" t="n">
+        <v>0</v>
+      </c>
+      <c r="M894" t="n">
+        <v>0</v>
+      </c>
+      <c r="N894" t="n">
+        <v>0</v>
+      </c>
+      <c r="O894" t="n">
+        <v>0</v>
+      </c>
+      <c r="P894" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q894" t="n">
+        <v>0</v>
+      </c>
+      <c r="R894" t="n">
+        <v>0</v>
+      </c>
+      <c r="S894" t="n">
+        <v>0</v>
+      </c>
+      <c r="T894" t="n">
+        <v>0</v>
+      </c>
+      <c r="U894" t="n">
+        <v>0</v>
+      </c>
+      <c r="V894" t="n">
+        <v>0</v>
+      </c>
+      <c r="W894" t="n">
+        <v>0</v>
+      </c>
+      <c r="X894" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y894" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z894" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C895" t="n">
+        <v>24</v>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>O. PEÑA LOPEZ</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="G895" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H895" t="n">
+        <v>30</v>
+      </c>
+      <c r="I895" t="n">
+        <v>0</v>
+      </c>
+      <c r="J895" t="n">
+        <v>0</v>
+      </c>
+      <c r="K895" t="n">
+        <v>0</v>
+      </c>
+      <c r="L895" t="n">
+        <v>0</v>
+      </c>
+      <c r="M895" t="n">
+        <v>0</v>
+      </c>
+      <c r="N895" t="n">
+        <v>2</v>
+      </c>
+      <c r="O895" t="n">
+        <v>0</v>
+      </c>
+      <c r="P895" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q895" t="n">
+        <v>0</v>
+      </c>
+      <c r="R895" t="n">
+        <v>0</v>
+      </c>
+      <c r="S895" t="n">
+        <v>0</v>
+      </c>
+      <c r="T895" t="n">
+        <v>0</v>
+      </c>
+      <c r="U895" t="n">
+        <v>0</v>
+      </c>
+      <c r="V895" t="n">
+        <v>0</v>
+      </c>
+      <c r="W895" t="n">
+        <v>0</v>
+      </c>
+      <c r="X895" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y895" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z895" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C896" t="n">
+        <v>24</v>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>P. RODRIGUEZ RIVERO</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="G896" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H896" t="n">
+        <v>132</v>
+      </c>
+      <c r="I896" t="n">
+        <v>0</v>
+      </c>
+      <c r="J896" t="n">
+        <v>0</v>
+      </c>
+      <c r="K896" t="n">
+        <v>0</v>
+      </c>
+      <c r="L896" t="n">
+        <v>0</v>
+      </c>
+      <c r="M896" t="n">
+        <v>0</v>
+      </c>
+      <c r="N896" t="n">
+        <v>0</v>
+      </c>
+      <c r="O896" t="n">
+        <v>0</v>
+      </c>
+      <c r="P896" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q896" t="n">
+        <v>0</v>
+      </c>
+      <c r="R896" t="n">
+        <v>0</v>
+      </c>
+      <c r="S896" t="n">
+        <v>0</v>
+      </c>
+      <c r="T896" t="n">
+        <v>0</v>
+      </c>
+      <c r="U896" t="n">
+        <v>0</v>
+      </c>
+      <c r="V896" t="n">
+        <v>0</v>
+      </c>
+      <c r="W896" t="n">
+        <v>0</v>
+      </c>
+      <c r="X896" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y896" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z896" t="n">
+        <v>-148.65</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C897" t="n">
+        <v>24</v>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>Y. RODRÍGUEZ MACHÍN</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="G897" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H897" t="n">
+        <v>93</v>
+      </c>
+      <c r="I897" t="n">
+        <v>0</v>
+      </c>
+      <c r="J897" t="n">
+        <v>1</v>
+      </c>
+      <c r="K897" t="n">
+        <v>0</v>
+      </c>
+      <c r="L897" t="n">
+        <v>0</v>
+      </c>
+      <c r="M897" t="n">
+        <v>0</v>
+      </c>
+      <c r="N897" t="n">
+        <v>0</v>
+      </c>
+      <c r="O897" t="n">
+        <v>0</v>
+      </c>
+      <c r="P897" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q897" t="n">
+        <v>0</v>
+      </c>
+      <c r="R897" t="n">
+        <v>0</v>
+      </c>
+      <c r="S897" t="n">
+        <v>0</v>
+      </c>
+      <c r="T897" t="n">
+        <v>0</v>
+      </c>
+      <c r="U897" t="n">
+        <v>0</v>
+      </c>
+      <c r="V897" t="n">
+        <v>0</v>
+      </c>
+      <c r="W897" t="n">
+        <v>0</v>
+      </c>
+      <c r="X897" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="Y897" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z897" t="n">
+        <v>-150</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C898" t="n">
+        <v>24</v>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>B. SCHUCH</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="G898" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H898" t="n">
+        <v>162</v>
+      </c>
+      <c r="I898" t="n">
+        <v>0</v>
+      </c>
+      <c r="J898" t="n">
+        <v>1</v>
+      </c>
+      <c r="K898" t="n">
+        <v>0</v>
+      </c>
+      <c r="L898" t="n">
+        <v>1</v>
+      </c>
+      <c r="M898" t="n">
+        <v>0</v>
+      </c>
+      <c r="N898" t="n">
+        <v>0</v>
+      </c>
+      <c r="O898" t="n">
+        <v>0</v>
+      </c>
+      <c r="P898" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q898" t="n">
+        <v>0</v>
+      </c>
+      <c r="R898" t="n">
+        <v>0</v>
+      </c>
+      <c r="S898" t="n">
+        <v>0</v>
+      </c>
+      <c r="T898" t="n">
+        <v>0</v>
+      </c>
+      <c r="U898" t="n">
+        <v>1</v>
+      </c>
+      <c r="V898" t="n">
+        <v>1</v>
+      </c>
+      <c r="W898" t="n">
+        <v>0</v>
+      </c>
+      <c r="X898" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="Y898" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z898" t="n">
+        <v>153.41</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C899" t="n">
+        <v>24</v>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>D. VAL GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="G899" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H899" t="n">
+        <v>162</v>
+      </c>
+      <c r="I899" t="n">
+        <v>0</v>
+      </c>
+      <c r="J899" t="n">
+        <v>2</v>
+      </c>
+      <c r="K899" t="n">
+        <v>1</v>
+      </c>
+      <c r="L899" t="n">
+        <v>2</v>
+      </c>
+      <c r="M899" t="n">
+        <v>1</v>
+      </c>
+      <c r="N899" t="n">
+        <v>0</v>
+      </c>
+      <c r="O899" t="n">
+        <v>0</v>
+      </c>
+      <c r="P899" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q899" t="n">
+        <v>0</v>
+      </c>
+      <c r="R899" t="n">
+        <v>0</v>
+      </c>
+      <c r="S899" t="n">
+        <v>0</v>
+      </c>
+      <c r="T899" t="n">
+        <v>0</v>
+      </c>
+      <c r="U899" t="n">
+        <v>1</v>
+      </c>
+      <c r="V899" t="n">
+        <v>0</v>
+      </c>
+      <c r="W899" t="n">
+        <v>1</v>
+      </c>
+      <c r="X899" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="Y899" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z899" t="n">
+        <v>153.41</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C900" t="n">
+        <v>24</v>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>G. GOMA</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="G900" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H900" t="n">
+        <v>162</v>
+      </c>
+      <c r="I900" t="n">
+        <v>0</v>
+      </c>
+      <c r="J900" t="n">
+        <v>0</v>
+      </c>
+      <c r="K900" t="n">
+        <v>0</v>
+      </c>
+      <c r="L900" t="n">
+        <v>0</v>
+      </c>
+      <c r="M900" t="n">
+        <v>0</v>
+      </c>
+      <c r="N900" t="n">
+        <v>0</v>
+      </c>
+      <c r="O900" t="n">
+        <v>0</v>
+      </c>
+      <c r="P900" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q900" t="n">
+        <v>0</v>
+      </c>
+      <c r="R900" t="n">
+        <v>0</v>
+      </c>
+      <c r="S900" t="n">
+        <v>0</v>
+      </c>
+      <c r="T900" t="n">
+        <v>1</v>
+      </c>
+      <c r="U900" t="n">
+        <v>2</v>
+      </c>
+      <c r="V900" t="n">
+        <v>2</v>
+      </c>
+      <c r="W900" t="n">
+        <v>0</v>
+      </c>
+      <c r="X900" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y900" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z900" t="n">
+        <v>153.41</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C901" t="n">
+        <v>24</v>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>J. VAQUERO PASCUAL</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="G901" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H901" t="n">
+        <v>162</v>
+      </c>
+      <c r="I901" t="n">
+        <v>0</v>
+      </c>
+      <c r="J901" t="n">
+        <v>1</v>
+      </c>
+      <c r="K901" t="n">
+        <v>1</v>
+      </c>
+      <c r="L901" t="n">
+        <v>0</v>
+      </c>
+      <c r="M901" t="n">
+        <v>0</v>
+      </c>
+      <c r="N901" t="n">
+        <v>1</v>
+      </c>
+      <c r="O901" t="n">
+        <v>1</v>
+      </c>
+      <c r="P901" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q901" t="n">
+        <v>0</v>
+      </c>
+      <c r="R901" t="n">
+        <v>0</v>
+      </c>
+      <c r="S901" t="n">
+        <v>0</v>
+      </c>
+      <c r="T901" t="n">
+        <v>0</v>
+      </c>
+      <c r="U901" t="n">
+        <v>0</v>
+      </c>
+      <c r="V901" t="n">
+        <v>0</v>
+      </c>
+      <c r="W901" t="n">
+        <v>0</v>
+      </c>
+      <c r="X901" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="Y901" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z901" t="n">
+        <v>153.41</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C902" t="n">
+        <v>24</v>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>M. ESTAPE ROIZ</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="G902" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H902" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="I902" t="n">
+        <v>0</v>
+      </c>
+      <c r="J902" t="n">
+        <v>1</v>
+      </c>
+      <c r="K902" t="n">
+        <v>0</v>
+      </c>
+      <c r="L902" t="n">
+        <v>0</v>
+      </c>
+      <c r="M902" t="n">
+        <v>0</v>
+      </c>
+      <c r="N902" t="n">
+        <v>0</v>
+      </c>
+      <c r="O902" t="n">
+        <v>0</v>
+      </c>
+      <c r="P902" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q902" t="n">
+        <v>0</v>
+      </c>
+      <c r="R902" t="n">
+        <v>0</v>
+      </c>
+      <c r="S902" t="n">
+        <v>0</v>
+      </c>
+      <c r="T902" t="n">
+        <v>0</v>
+      </c>
+      <c r="U902" t="n">
+        <v>0</v>
+      </c>
+      <c r="V902" t="n">
+        <v>0</v>
+      </c>
+      <c r="W902" t="n">
+        <v>0</v>
+      </c>
+      <c r="X902" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y902" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z902" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C903" t="n">
+        <v>24</v>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>T. VERDERA BENASSAR</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="G903" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H903" t="n">
+        <v>85.19999999999999</v>
+      </c>
+      <c r="I903" t="n">
+        <v>0</v>
+      </c>
+      <c r="J903" t="n">
+        <v>1</v>
+      </c>
+      <c r="K903" t="n">
+        <v>0</v>
+      </c>
+      <c r="L903" t="n">
+        <v>0</v>
+      </c>
+      <c r="M903" t="n">
+        <v>0</v>
+      </c>
+      <c r="N903" t="n">
+        <v>0</v>
+      </c>
+      <c r="O903" t="n">
+        <v>0</v>
+      </c>
+      <c r="P903" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q903" t="n">
+        <v>0</v>
+      </c>
+      <c r="R903" t="n">
+        <v>1</v>
+      </c>
+      <c r="S903" t="n">
+        <v>0</v>
+      </c>
+      <c r="T903" t="n">
+        <v>1</v>
+      </c>
+      <c r="U903" t="n">
+        <v>0</v>
+      </c>
+      <c r="V903" t="n">
+        <v>0</v>
+      </c>
+      <c r="W903" t="n">
+        <v>0</v>
+      </c>
+      <c r="X903" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="Y903" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z903" t="n">
+        <v>174.42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/3FEB_25_26/clutch_data_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/clutch_data_25_26_3FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z903"/>
+  <dimension ref="A1:Z931"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81740,6 +81740,2526 @@
         <v>174.42</v>
       </c>
     </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C904" t="n">
+        <v>23</v>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="G904" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="H904" t="n">
+        <v>286.2</v>
+      </c>
+      <c r="I904" t="n">
+        <v>0</v>
+      </c>
+      <c r="J904" t="n">
+        <v>1</v>
+      </c>
+      <c r="K904" t="n">
+        <v>1</v>
+      </c>
+      <c r="L904" t="n">
+        <v>1</v>
+      </c>
+      <c r="M904" t="n">
+        <v>1</v>
+      </c>
+      <c r="N904" t="n">
+        <v>0</v>
+      </c>
+      <c r="O904" t="n">
+        <v>0</v>
+      </c>
+      <c r="P904" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q904" t="n">
+        <v>0</v>
+      </c>
+      <c r="R904" t="n">
+        <v>0</v>
+      </c>
+      <c r="S904" t="n">
+        <v>0</v>
+      </c>
+      <c r="T904" t="n">
+        <v>0</v>
+      </c>
+      <c r="U904" t="n">
+        <v>1</v>
+      </c>
+      <c r="V904" t="n">
+        <v>1</v>
+      </c>
+      <c r="W904" t="n">
+        <v>0</v>
+      </c>
+      <c r="X904" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y904" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z904" t="n">
+        <v>-5.63</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C905" t="n">
+        <v>23</v>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>A. JIMENEZ FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="G905" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H905" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="I905" t="n">
+        <v>0</v>
+      </c>
+      <c r="J905" t="n">
+        <v>0</v>
+      </c>
+      <c r="K905" t="n">
+        <v>0</v>
+      </c>
+      <c r="L905" t="n">
+        <v>0</v>
+      </c>
+      <c r="M905" t="n">
+        <v>0</v>
+      </c>
+      <c r="N905" t="n">
+        <v>0</v>
+      </c>
+      <c r="O905" t="n">
+        <v>0</v>
+      </c>
+      <c r="P905" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q905" t="n">
+        <v>0</v>
+      </c>
+      <c r="R905" t="n">
+        <v>0</v>
+      </c>
+      <c r="S905" t="n">
+        <v>0</v>
+      </c>
+      <c r="T905" t="n">
+        <v>0</v>
+      </c>
+      <c r="U905" t="n">
+        <v>0</v>
+      </c>
+      <c r="V905" t="n">
+        <v>0</v>
+      </c>
+      <c r="W905" t="n">
+        <v>0</v>
+      </c>
+      <c r="X905" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y905" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z905" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C906" t="n">
+        <v>23</v>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>D. RODRIGUEZ GARCIA</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="G906" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="H906" t="n">
+        <v>286.2</v>
+      </c>
+      <c r="I906" t="n">
+        <v>0</v>
+      </c>
+      <c r="J906" t="n">
+        <v>2</v>
+      </c>
+      <c r="K906" t="n">
+        <v>0</v>
+      </c>
+      <c r="L906" t="n">
+        <v>1</v>
+      </c>
+      <c r="M906" t="n">
+        <v>0</v>
+      </c>
+      <c r="N906" t="n">
+        <v>0</v>
+      </c>
+      <c r="O906" t="n">
+        <v>0</v>
+      </c>
+      <c r="P906" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q906" t="n">
+        <v>0</v>
+      </c>
+      <c r="R906" t="n">
+        <v>0</v>
+      </c>
+      <c r="S906" t="n">
+        <v>0</v>
+      </c>
+      <c r="T906" t="n">
+        <v>0</v>
+      </c>
+      <c r="U906" t="n">
+        <v>0</v>
+      </c>
+      <c r="V906" t="n">
+        <v>0</v>
+      </c>
+      <c r="W906" t="n">
+        <v>0</v>
+      </c>
+      <c r="X906" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y906" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z906" t="n">
+        <v>-5.63</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C907" t="n">
+        <v>23</v>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>J. RIES</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="G907" t="n">
+        <v>4</v>
+      </c>
+      <c r="H907" t="n">
+        <v>240</v>
+      </c>
+      <c r="I907" t="n">
+        <v>0</v>
+      </c>
+      <c r="J907" t="n">
+        <v>3</v>
+      </c>
+      <c r="K907" t="n">
+        <v>1</v>
+      </c>
+      <c r="L907" t="n">
+        <v>2</v>
+      </c>
+      <c r="M907" t="n">
+        <v>1</v>
+      </c>
+      <c r="N907" t="n">
+        <v>0</v>
+      </c>
+      <c r="O907" t="n">
+        <v>0</v>
+      </c>
+      <c r="P907" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q907" t="n">
+        <v>0</v>
+      </c>
+      <c r="R907" t="n">
+        <v>0</v>
+      </c>
+      <c r="S907" t="n">
+        <v>0</v>
+      </c>
+      <c r="T907" t="n">
+        <v>1</v>
+      </c>
+      <c r="U907" t="n">
+        <v>1</v>
+      </c>
+      <c r="V907" t="n">
+        <v>0</v>
+      </c>
+      <c r="W907" t="n">
+        <v>1</v>
+      </c>
+      <c r="X907" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="Y907" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z907" t="n">
+        <v>16.57</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C908" t="n">
+        <v>23</v>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>M. NIANG</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="G908" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H908" t="n">
+        <v>282</v>
+      </c>
+      <c r="I908" t="n">
+        <v>0</v>
+      </c>
+      <c r="J908" t="n">
+        <v>3</v>
+      </c>
+      <c r="K908" t="n">
+        <v>1</v>
+      </c>
+      <c r="L908" t="n">
+        <v>0</v>
+      </c>
+      <c r="M908" t="n">
+        <v>0</v>
+      </c>
+      <c r="N908" t="n">
+        <v>0</v>
+      </c>
+      <c r="O908" t="n">
+        <v>0</v>
+      </c>
+      <c r="P908" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Q908" t="n">
+        <v>0</v>
+      </c>
+      <c r="R908" t="n">
+        <v>0</v>
+      </c>
+      <c r="S908" t="n">
+        <v>1</v>
+      </c>
+      <c r="T908" t="n">
+        <v>0</v>
+      </c>
+      <c r="U908" t="n">
+        <v>2</v>
+      </c>
+      <c r="V908" t="n">
+        <v>1</v>
+      </c>
+      <c r="W908" t="n">
+        <v>1</v>
+      </c>
+      <c r="X908" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y908" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z908" t="n">
+        <v>-43.13</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C909" t="n">
+        <v>23</v>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>P. RODRIGUEZ RIVERO</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="G909" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="H909" t="n">
+        <v>286.2</v>
+      </c>
+      <c r="I909" t="n">
+        <v>0</v>
+      </c>
+      <c r="J909" t="n">
+        <v>2</v>
+      </c>
+      <c r="K909" t="n">
+        <v>1</v>
+      </c>
+      <c r="L909" t="n">
+        <v>1</v>
+      </c>
+      <c r="M909" t="n">
+        <v>0</v>
+      </c>
+      <c r="N909" t="n">
+        <v>0</v>
+      </c>
+      <c r="O909" t="n">
+        <v>0</v>
+      </c>
+      <c r="P909" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q909" t="n">
+        <v>0</v>
+      </c>
+      <c r="R909" t="n">
+        <v>1</v>
+      </c>
+      <c r="S909" t="n">
+        <v>0</v>
+      </c>
+      <c r="T909" t="n">
+        <v>0</v>
+      </c>
+      <c r="U909" t="n">
+        <v>1</v>
+      </c>
+      <c r="V909" t="n">
+        <v>0</v>
+      </c>
+      <c r="W909" t="n">
+        <v>1</v>
+      </c>
+      <c r="X909" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y909" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z909" t="n">
+        <v>-5.63</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C910" t="n">
+        <v>23</v>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="G910" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H910" t="n">
+        <v>79.80000000000001</v>
+      </c>
+      <c r="I910" t="n">
+        <v>0</v>
+      </c>
+      <c r="J910" t="n">
+        <v>0</v>
+      </c>
+      <c r="K910" t="n">
+        <v>0</v>
+      </c>
+      <c r="L910" t="n">
+        <v>0</v>
+      </c>
+      <c r="M910" t="n">
+        <v>0</v>
+      </c>
+      <c r="N910" t="n">
+        <v>0</v>
+      </c>
+      <c r="O910" t="n">
+        <v>0</v>
+      </c>
+      <c r="P910" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q910" t="n">
+        <v>0</v>
+      </c>
+      <c r="R910" t="n">
+        <v>0</v>
+      </c>
+      <c r="S910" t="n">
+        <v>0</v>
+      </c>
+      <c r="T910" t="n">
+        <v>0</v>
+      </c>
+      <c r="U910" t="n">
+        <v>0</v>
+      </c>
+      <c r="V910" t="n">
+        <v>0</v>
+      </c>
+      <c r="W910" t="n">
+        <v>0</v>
+      </c>
+      <c r="X910" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y910" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z910" t="n">
+        <v>53.79</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C911" t="n">
+        <v>23</v>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>B. FERNANDEZ SHEPHARD</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="G911" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="H911" t="n">
+        <v>226.8</v>
+      </c>
+      <c r="I911" t="n">
+        <v>0</v>
+      </c>
+      <c r="J911" t="n">
+        <v>1</v>
+      </c>
+      <c r="K911" t="n">
+        <v>0</v>
+      </c>
+      <c r="L911" t="n">
+        <v>1</v>
+      </c>
+      <c r="M911" t="n">
+        <v>0</v>
+      </c>
+      <c r="N911" t="n">
+        <v>0</v>
+      </c>
+      <c r="O911" t="n">
+        <v>0</v>
+      </c>
+      <c r="P911" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q911" t="n">
+        <v>0</v>
+      </c>
+      <c r="R911" t="n">
+        <v>0</v>
+      </c>
+      <c r="S911" t="n">
+        <v>0</v>
+      </c>
+      <c r="T911" t="n">
+        <v>0</v>
+      </c>
+      <c r="U911" t="n">
+        <v>0</v>
+      </c>
+      <c r="V911" t="n">
+        <v>0</v>
+      </c>
+      <c r="W911" t="n">
+        <v>0</v>
+      </c>
+      <c r="X911" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="Y911" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z911" t="n">
+        <v>-28.62</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C912" t="n">
+        <v>23</v>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>E. DUQUE NEGRÍN</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="G912" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H912" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="I912" t="n">
+        <v>0</v>
+      </c>
+      <c r="J912" t="n">
+        <v>2</v>
+      </c>
+      <c r="K912" t="n">
+        <v>1</v>
+      </c>
+      <c r="L912" t="n">
+        <v>0</v>
+      </c>
+      <c r="M912" t="n">
+        <v>0</v>
+      </c>
+      <c r="N912" t="n">
+        <v>6</v>
+      </c>
+      <c r="O912" t="n">
+        <v>3</v>
+      </c>
+      <c r="P912" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q912" t="n">
+        <v>0</v>
+      </c>
+      <c r="R912" t="n">
+        <v>0</v>
+      </c>
+      <c r="S912" t="n">
+        <v>0</v>
+      </c>
+      <c r="T912" t="n">
+        <v>1</v>
+      </c>
+      <c r="U912" t="n">
+        <v>0</v>
+      </c>
+      <c r="V912" t="n">
+        <v>0</v>
+      </c>
+      <c r="W912" t="n">
+        <v>0</v>
+      </c>
+      <c r="X912" t="n">
+        <v>232</v>
+      </c>
+      <c r="Y912" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z912" t="n">
+        <v>-66.67</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C913" t="n">
+        <v>23</v>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>J. GALLETTO LAMELA</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="G913" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H913" t="n">
+        <v>174</v>
+      </c>
+      <c r="I913" t="n">
+        <v>0</v>
+      </c>
+      <c r="J913" t="n">
+        <v>0</v>
+      </c>
+      <c r="K913" t="n">
+        <v>0</v>
+      </c>
+      <c r="L913" t="n">
+        <v>0</v>
+      </c>
+      <c r="M913" t="n">
+        <v>0</v>
+      </c>
+      <c r="N913" t="n">
+        <v>0</v>
+      </c>
+      <c r="O913" t="n">
+        <v>0</v>
+      </c>
+      <c r="P913" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q913" t="n">
+        <v>0</v>
+      </c>
+      <c r="R913" t="n">
+        <v>0</v>
+      </c>
+      <c r="S913" t="n">
+        <v>1</v>
+      </c>
+      <c r="T913" t="n">
+        <v>0</v>
+      </c>
+      <c r="U913" t="n">
+        <v>1</v>
+      </c>
+      <c r="V913" t="n">
+        <v>0</v>
+      </c>
+      <c r="W913" t="n">
+        <v>1</v>
+      </c>
+      <c r="X913" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y913" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z913" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C914" t="n">
+        <v>23</v>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>K. RIVEROL DE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="G914" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H914" t="n">
+        <v>220.2</v>
+      </c>
+      <c r="I914" t="n">
+        <v>0</v>
+      </c>
+      <c r="J914" t="n">
+        <v>1</v>
+      </c>
+      <c r="K914" t="n">
+        <v>0</v>
+      </c>
+      <c r="L914" t="n">
+        <v>1</v>
+      </c>
+      <c r="M914" t="n">
+        <v>0</v>
+      </c>
+      <c r="N914" t="n">
+        <v>0</v>
+      </c>
+      <c r="O914" t="n">
+        <v>0</v>
+      </c>
+      <c r="P914" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q914" t="n">
+        <v>0</v>
+      </c>
+      <c r="R914" t="n">
+        <v>0</v>
+      </c>
+      <c r="S914" t="n">
+        <v>0</v>
+      </c>
+      <c r="T914" t="n">
+        <v>0</v>
+      </c>
+      <c r="U914" t="n">
+        <v>1</v>
+      </c>
+      <c r="V914" t="n">
+        <v>1</v>
+      </c>
+      <c r="W914" t="n">
+        <v>0</v>
+      </c>
+      <c r="X914" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="Y914" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z914" t="n">
+        <v>-50.94</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C915" t="n">
+        <v>23</v>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>M. KHIVRENKO</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="G915" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H915" t="n">
+        <v>282</v>
+      </c>
+      <c r="I915" t="n">
+        <v>0</v>
+      </c>
+      <c r="J915" t="n">
+        <v>0</v>
+      </c>
+      <c r="K915" t="n">
+        <v>0</v>
+      </c>
+      <c r="L915" t="n">
+        <v>0</v>
+      </c>
+      <c r="M915" t="n">
+        <v>0</v>
+      </c>
+      <c r="N915" t="n">
+        <v>2</v>
+      </c>
+      <c r="O915" t="n">
+        <v>1</v>
+      </c>
+      <c r="P915" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q915" t="n">
+        <v>0</v>
+      </c>
+      <c r="R915" t="n">
+        <v>0</v>
+      </c>
+      <c r="S915" t="n">
+        <v>0</v>
+      </c>
+      <c r="T915" t="n">
+        <v>0</v>
+      </c>
+      <c r="U915" t="n">
+        <v>4</v>
+      </c>
+      <c r="V915" t="n">
+        <v>2</v>
+      </c>
+      <c r="W915" t="n">
+        <v>2</v>
+      </c>
+      <c r="X915" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="Y915" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z915" t="n">
+        <v>43.13</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C916" t="n">
+        <v>23</v>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="G916" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H916" t="n">
+        <v>264</v>
+      </c>
+      <c r="I916" t="n">
+        <v>0</v>
+      </c>
+      <c r="J916" t="n">
+        <v>2</v>
+      </c>
+      <c r="K916" t="n">
+        <v>1</v>
+      </c>
+      <c r="L916" t="n">
+        <v>2</v>
+      </c>
+      <c r="M916" t="n">
+        <v>1</v>
+      </c>
+      <c r="N916" t="n">
+        <v>0</v>
+      </c>
+      <c r="O916" t="n">
+        <v>0</v>
+      </c>
+      <c r="P916" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q916" t="n">
+        <v>0</v>
+      </c>
+      <c r="R916" t="n">
+        <v>0</v>
+      </c>
+      <c r="S916" t="n">
+        <v>0</v>
+      </c>
+      <c r="T916" t="n">
+        <v>0</v>
+      </c>
+      <c r="U916" t="n">
+        <v>1</v>
+      </c>
+      <c r="V916" t="n">
+        <v>0</v>
+      </c>
+      <c r="W916" t="n">
+        <v>1</v>
+      </c>
+      <c r="X916" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="Y916" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z916" t="n">
+        <v>19.68</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C917" t="n">
+        <v>23</v>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>P. HERNANDEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="G917" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H917" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="I917" t="n">
+        <v>0</v>
+      </c>
+      <c r="J917" t="n">
+        <v>0</v>
+      </c>
+      <c r="K917" t="n">
+        <v>0</v>
+      </c>
+      <c r="L917" t="n">
+        <v>0</v>
+      </c>
+      <c r="M917" t="n">
+        <v>0</v>
+      </c>
+      <c r="N917" t="n">
+        <v>0</v>
+      </c>
+      <c r="O917" t="n">
+        <v>0</v>
+      </c>
+      <c r="P917" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q917" t="n">
+        <v>0</v>
+      </c>
+      <c r="R917" t="n">
+        <v>0</v>
+      </c>
+      <c r="S917" t="n">
+        <v>0</v>
+      </c>
+      <c r="T917" t="n">
+        <v>0</v>
+      </c>
+      <c r="U917" t="n">
+        <v>0</v>
+      </c>
+      <c r="V917" t="n">
+        <v>0</v>
+      </c>
+      <c r="W917" t="n">
+        <v>0</v>
+      </c>
+      <c r="X917" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y917" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z917" t="n">
+        <v>133.33</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C918" t="n">
+        <v>24</v>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>A. VICENTE VIANA</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="G918" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H918" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="I918" t="n">
+        <v>0</v>
+      </c>
+      <c r="J918" t="n">
+        <v>0</v>
+      </c>
+      <c r="K918" t="n">
+        <v>0</v>
+      </c>
+      <c r="L918" t="n">
+        <v>0</v>
+      </c>
+      <c r="M918" t="n">
+        <v>0</v>
+      </c>
+      <c r="N918" t="n">
+        <v>0</v>
+      </c>
+      <c r="O918" t="n">
+        <v>0</v>
+      </c>
+      <c r="P918" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q918" t="n">
+        <v>0</v>
+      </c>
+      <c r="R918" t="n">
+        <v>0</v>
+      </c>
+      <c r="S918" t="n">
+        <v>1</v>
+      </c>
+      <c r="T918" t="n">
+        <v>0</v>
+      </c>
+      <c r="U918" t="n">
+        <v>0</v>
+      </c>
+      <c r="V918" t="n">
+        <v>0</v>
+      </c>
+      <c r="W918" t="n">
+        <v>0</v>
+      </c>
+      <c r="X918" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y918" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z918" t="n">
+        <v>-68.7</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C919" t="n">
+        <v>24</v>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>B. GUEYE</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="G919" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H919" t="n">
+        <v>75</v>
+      </c>
+      <c r="I919" t="n">
+        <v>0</v>
+      </c>
+      <c r="J919" t="n">
+        <v>0</v>
+      </c>
+      <c r="K919" t="n">
+        <v>0</v>
+      </c>
+      <c r="L919" t="n">
+        <v>0</v>
+      </c>
+      <c r="M919" t="n">
+        <v>0</v>
+      </c>
+      <c r="N919" t="n">
+        <v>0</v>
+      </c>
+      <c r="O919" t="n">
+        <v>0</v>
+      </c>
+      <c r="P919" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q919" t="n">
+        <v>0</v>
+      </c>
+      <c r="R919" t="n">
+        <v>0</v>
+      </c>
+      <c r="S919" t="n">
+        <v>0</v>
+      </c>
+      <c r="T919" t="n">
+        <v>0</v>
+      </c>
+      <c r="U919" t="n">
+        <v>0</v>
+      </c>
+      <c r="V919" t="n">
+        <v>0</v>
+      </c>
+      <c r="W919" t="n">
+        <v>0</v>
+      </c>
+      <c r="X919" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y919" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z919" t="n">
+        <v>30.56</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C920" t="n">
+        <v>24</v>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>C. KLOTZ MAROTO</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="G920" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H920" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="I920" t="n">
+        <v>0</v>
+      </c>
+      <c r="J920" t="n">
+        <v>0</v>
+      </c>
+      <c r="K920" t="n">
+        <v>0</v>
+      </c>
+      <c r="L920" t="n">
+        <v>0</v>
+      </c>
+      <c r="M920" t="n">
+        <v>0</v>
+      </c>
+      <c r="N920" t="n">
+        <v>0</v>
+      </c>
+      <c r="O920" t="n">
+        <v>0</v>
+      </c>
+      <c r="P920" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q920" t="n">
+        <v>0</v>
+      </c>
+      <c r="R920" t="n">
+        <v>0</v>
+      </c>
+      <c r="S920" t="n">
+        <v>0</v>
+      </c>
+      <c r="T920" t="n">
+        <v>0</v>
+      </c>
+      <c r="U920" t="n">
+        <v>1</v>
+      </c>
+      <c r="V920" t="n">
+        <v>1</v>
+      </c>
+      <c r="W920" t="n">
+        <v>0</v>
+      </c>
+      <c r="X920" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y920" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z920" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C921" t="n">
+        <v>24</v>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>C. UNANUE CEGARRA</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="G921" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H921" t="n">
+        <v>246</v>
+      </c>
+      <c r="I921" t="n">
+        <v>0</v>
+      </c>
+      <c r="J921" t="n">
+        <v>4</v>
+      </c>
+      <c r="K921" t="n">
+        <v>2</v>
+      </c>
+      <c r="L921" t="n">
+        <v>3</v>
+      </c>
+      <c r="M921" t="n">
+        <v>1</v>
+      </c>
+      <c r="N921" t="n">
+        <v>0</v>
+      </c>
+      <c r="O921" t="n">
+        <v>0</v>
+      </c>
+      <c r="P921" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Q921" t="n">
+        <v>0</v>
+      </c>
+      <c r="R921" t="n">
+        <v>0</v>
+      </c>
+      <c r="S921" t="n">
+        <v>1</v>
+      </c>
+      <c r="T921" t="n">
+        <v>0</v>
+      </c>
+      <c r="U921" t="n">
+        <v>0</v>
+      </c>
+      <c r="V921" t="n">
+        <v>0</v>
+      </c>
+      <c r="W921" t="n">
+        <v>0</v>
+      </c>
+      <c r="X921" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="Y921" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z921" t="n">
+        <v>-44.92</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C922" t="n">
+        <v>24</v>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>D. LORENZO NEGRETE</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="G922" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H922" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="I922" t="n">
+        <v>0</v>
+      </c>
+      <c r="J922" t="n">
+        <v>2</v>
+      </c>
+      <c r="K922" t="n">
+        <v>1</v>
+      </c>
+      <c r="L922" t="n">
+        <v>1</v>
+      </c>
+      <c r="M922" t="n">
+        <v>0</v>
+      </c>
+      <c r="N922" t="n">
+        <v>0</v>
+      </c>
+      <c r="O922" t="n">
+        <v>0</v>
+      </c>
+      <c r="P922" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q922" t="n">
+        <v>0</v>
+      </c>
+      <c r="R922" t="n">
+        <v>0</v>
+      </c>
+      <c r="S922" t="n">
+        <v>1</v>
+      </c>
+      <c r="T922" t="n">
+        <v>0</v>
+      </c>
+      <c r="U922" t="n">
+        <v>1</v>
+      </c>
+      <c r="V922" t="n">
+        <v>1</v>
+      </c>
+      <c r="W922" t="n">
+        <v>0</v>
+      </c>
+      <c r="X922" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y922" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z922" t="n">
+        <v>-47.37</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C923" t="n">
+        <v>24</v>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>J. FRANCES PASCUAL</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="G923" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H923" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="I923" t="n">
+        <v>0</v>
+      </c>
+      <c r="J923" t="n">
+        <v>2</v>
+      </c>
+      <c r="K923" t="n">
+        <v>0</v>
+      </c>
+      <c r="L923" t="n">
+        <v>0</v>
+      </c>
+      <c r="M923" t="n">
+        <v>0</v>
+      </c>
+      <c r="N923" t="n">
+        <v>0</v>
+      </c>
+      <c r="O923" t="n">
+        <v>0</v>
+      </c>
+      <c r="P923" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q923" t="n">
+        <v>0</v>
+      </c>
+      <c r="R923" t="n">
+        <v>0</v>
+      </c>
+      <c r="S923" t="n">
+        <v>1</v>
+      </c>
+      <c r="T923" t="n">
+        <v>0</v>
+      </c>
+      <c r="U923" t="n">
+        <v>1</v>
+      </c>
+      <c r="V923" t="n">
+        <v>0</v>
+      </c>
+      <c r="W923" t="n">
+        <v>1</v>
+      </c>
+      <c r="X923" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y923" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z923" t="n">
+        <v>-47.37</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C924" t="n">
+        <v>24</v>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>S. GACIC</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="G924" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H924" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="I924" t="n">
+        <v>0</v>
+      </c>
+      <c r="J924" t="n">
+        <v>0</v>
+      </c>
+      <c r="K924" t="n">
+        <v>0</v>
+      </c>
+      <c r="L924" t="n">
+        <v>0</v>
+      </c>
+      <c r="M924" t="n">
+        <v>0</v>
+      </c>
+      <c r="N924" t="n">
+        <v>0</v>
+      </c>
+      <c r="O924" t="n">
+        <v>0</v>
+      </c>
+      <c r="P924" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q924" t="n">
+        <v>0</v>
+      </c>
+      <c r="R924" t="n">
+        <v>0</v>
+      </c>
+      <c r="S924" t="n">
+        <v>1</v>
+      </c>
+      <c r="T924" t="n">
+        <v>0</v>
+      </c>
+      <c r="U924" t="n">
+        <v>3</v>
+      </c>
+      <c r="V924" t="n">
+        <v>1</v>
+      </c>
+      <c r="W924" t="n">
+        <v>2</v>
+      </c>
+      <c r="X924" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y924" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z924" t="n">
+        <v>-47.37</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C925" t="n">
+        <v>24</v>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>V. ALONSO PASCUAL</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="G925" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H925" t="n">
+        <v>87</v>
+      </c>
+      <c r="I925" t="n">
+        <v>0</v>
+      </c>
+      <c r="J925" t="n">
+        <v>0</v>
+      </c>
+      <c r="K925" t="n">
+        <v>0</v>
+      </c>
+      <c r="L925" t="n">
+        <v>0</v>
+      </c>
+      <c r="M925" t="n">
+        <v>0</v>
+      </c>
+      <c r="N925" t="n">
+        <v>0</v>
+      </c>
+      <c r="O925" t="n">
+        <v>0</v>
+      </c>
+      <c r="P925" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q925" t="n">
+        <v>0</v>
+      </c>
+      <c r="R925" t="n">
+        <v>1</v>
+      </c>
+      <c r="S925" t="n">
+        <v>0</v>
+      </c>
+      <c r="T925" t="n">
+        <v>0</v>
+      </c>
+      <c r="U925" t="n">
+        <v>0</v>
+      </c>
+      <c r="V925" t="n">
+        <v>0</v>
+      </c>
+      <c r="W925" t="n">
+        <v>0</v>
+      </c>
+      <c r="X925" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y925" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z925" t="n">
+        <v>-73.61</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C926" t="n">
+        <v>24</v>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>A. FERNÁNDEZ GÓMEZ</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="G926" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H926" t="n">
+        <v>267</v>
+      </c>
+      <c r="I926" t="n">
+        <v>0</v>
+      </c>
+      <c r="J926" t="n">
+        <v>3</v>
+      </c>
+      <c r="K926" t="n">
+        <v>1</v>
+      </c>
+      <c r="L926" t="n">
+        <v>1</v>
+      </c>
+      <c r="M926" t="n">
+        <v>0</v>
+      </c>
+      <c r="N926" t="n">
+        <v>4</v>
+      </c>
+      <c r="O926" t="n">
+        <v>3</v>
+      </c>
+      <c r="P926" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Q926" t="n">
+        <v>0</v>
+      </c>
+      <c r="R926" t="n">
+        <v>1</v>
+      </c>
+      <c r="S926" t="n">
+        <v>0</v>
+      </c>
+      <c r="T926" t="n">
+        <v>2</v>
+      </c>
+      <c r="U926" t="n">
+        <v>0</v>
+      </c>
+      <c r="V926" t="n">
+        <v>0</v>
+      </c>
+      <c r="W926" t="n">
+        <v>0</v>
+      </c>
+      <c r="X926" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="Y926" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z926" t="n">
+        <v>39.59</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C927" t="n">
+        <v>24</v>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>A. MARTIN GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="G927" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H927" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="I927" t="n">
+        <v>0</v>
+      </c>
+      <c r="J927" t="n">
+        <v>0</v>
+      </c>
+      <c r="K927" t="n">
+        <v>0</v>
+      </c>
+      <c r="L927" t="n">
+        <v>0</v>
+      </c>
+      <c r="M927" t="n">
+        <v>0</v>
+      </c>
+      <c r="N927" t="n">
+        <v>0</v>
+      </c>
+      <c r="O927" t="n">
+        <v>0</v>
+      </c>
+      <c r="P927" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q927" t="n">
+        <v>0</v>
+      </c>
+      <c r="R927" t="n">
+        <v>0</v>
+      </c>
+      <c r="S927" t="n">
+        <v>0</v>
+      </c>
+      <c r="T927" t="n">
+        <v>0</v>
+      </c>
+      <c r="U927" t="n">
+        <v>0</v>
+      </c>
+      <c r="V927" t="n">
+        <v>0</v>
+      </c>
+      <c r="W927" t="n">
+        <v>0</v>
+      </c>
+      <c r="X927" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y927" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z927" t="n">
+        <v>106.38</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C928" t="n">
+        <v>24</v>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>A. SANTANA OJEDA</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="G928" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H928" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="I928" t="n">
+        <v>0</v>
+      </c>
+      <c r="J928" t="n">
+        <v>2</v>
+      </c>
+      <c r="K928" t="n">
+        <v>0</v>
+      </c>
+      <c r="L928" t="n">
+        <v>0</v>
+      </c>
+      <c r="M928" t="n">
+        <v>0</v>
+      </c>
+      <c r="N928" t="n">
+        <v>0</v>
+      </c>
+      <c r="O928" t="n">
+        <v>0</v>
+      </c>
+      <c r="P928" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q928" t="n">
+        <v>0</v>
+      </c>
+      <c r="R928" t="n">
+        <v>1</v>
+      </c>
+      <c r="S928" t="n">
+        <v>0</v>
+      </c>
+      <c r="T928" t="n">
+        <v>1</v>
+      </c>
+      <c r="U928" t="n">
+        <v>0</v>
+      </c>
+      <c r="V928" t="n">
+        <v>0</v>
+      </c>
+      <c r="W928" t="n">
+        <v>0</v>
+      </c>
+      <c r="X928" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="Y928" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z928" t="n">
+        <v>47.37</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C929" t="n">
+        <v>24</v>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>A. VIDAL RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="G929" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H929" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="I929" t="n">
+        <v>0</v>
+      </c>
+      <c r="J929" t="n">
+        <v>2</v>
+      </c>
+      <c r="K929" t="n">
+        <v>1</v>
+      </c>
+      <c r="L929" t="n">
+        <v>0</v>
+      </c>
+      <c r="M929" t="n">
+        <v>0</v>
+      </c>
+      <c r="N929" t="n">
+        <v>2</v>
+      </c>
+      <c r="O929" t="n">
+        <v>2</v>
+      </c>
+      <c r="P929" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q929" t="n">
+        <v>0</v>
+      </c>
+      <c r="R929" t="n">
+        <v>0</v>
+      </c>
+      <c r="S929" t="n">
+        <v>0</v>
+      </c>
+      <c r="T929" t="n">
+        <v>0</v>
+      </c>
+      <c r="U929" t="n">
+        <v>3</v>
+      </c>
+      <c r="V929" t="n">
+        <v>2</v>
+      </c>
+      <c r="W929" t="n">
+        <v>1</v>
+      </c>
+      <c r="X929" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="Y929" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z929" t="n">
+        <v>47.37</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C930" t="n">
+        <v>24</v>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>G. ARTILES ROMERO</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="G930" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H930" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="I930" t="n">
+        <v>0</v>
+      </c>
+      <c r="J930" t="n">
+        <v>0</v>
+      </c>
+      <c r="K930" t="n">
+        <v>0</v>
+      </c>
+      <c r="L930" t="n">
+        <v>0</v>
+      </c>
+      <c r="M930" t="n">
+        <v>0</v>
+      </c>
+      <c r="N930" t="n">
+        <v>2</v>
+      </c>
+      <c r="O930" t="n">
+        <v>1</v>
+      </c>
+      <c r="P930" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q930" t="n">
+        <v>0</v>
+      </c>
+      <c r="R930" t="n">
+        <v>0</v>
+      </c>
+      <c r="S930" t="n">
+        <v>0</v>
+      </c>
+      <c r="T930" t="n">
+        <v>2</v>
+      </c>
+      <c r="U930" t="n">
+        <v>0</v>
+      </c>
+      <c r="V930" t="n">
+        <v>0</v>
+      </c>
+      <c r="W930" t="n">
+        <v>0</v>
+      </c>
+      <c r="X930" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="Y930" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z930" t="n">
+        <v>47.37</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C931" t="n">
+        <v>24</v>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>J. JIMENEZ HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="G931" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="H931" t="n">
+        <v>261</v>
+      </c>
+      <c r="I931" t="n">
+        <v>0</v>
+      </c>
+      <c r="J931" t="n">
+        <v>0</v>
+      </c>
+      <c r="K931" t="n">
+        <v>0</v>
+      </c>
+      <c r="L931" t="n">
+        <v>0</v>
+      </c>
+      <c r="M931" t="n">
+        <v>0</v>
+      </c>
+      <c r="N931" t="n">
+        <v>0</v>
+      </c>
+      <c r="O931" t="n">
+        <v>0</v>
+      </c>
+      <c r="P931" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q931" t="n">
+        <v>0</v>
+      </c>
+      <c r="R931" t="n">
+        <v>0</v>
+      </c>
+      <c r="S931" t="n">
+        <v>1</v>
+      </c>
+      <c r="T931" t="n">
+        <v>0</v>
+      </c>
+      <c r="U931" t="n">
+        <v>0</v>
+      </c>
+      <c r="V931" t="n">
+        <v>0</v>
+      </c>
+      <c r="W931" t="n">
+        <v>0</v>
+      </c>
+      <c r="X931" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="Y931" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z931" t="n">
+        <v>42.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/3FEB_25_26/clutch_data_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/clutch_data_25_26_3FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1016"/>
+  <dimension ref="A1:Z1076"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91910,6 +91910,5406 @@
         <v>98.13</v>
       </c>
     </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1017" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>A. GOMEZ SERRANO</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="G1017" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H1017" t="n">
+        <v>93</v>
+      </c>
+      <c r="I1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1017" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1017" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1017" t="n">
+        <v>2</v>
+      </c>
+      <c r="O1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1017" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1017" t="n">
+        <v>65.28</v>
+      </c>
+      <c r="Y1017" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z1017" t="n">
+        <v>-61.11</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1018" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>A. OLMEDO VELASCO</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="G1018" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1018" t="n">
+        <v>240</v>
+      </c>
+      <c r="I1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1018" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1018" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1018" t="n">
+        <v>2</v>
+      </c>
+      <c r="O1018" t="n">
+        <v>2</v>
+      </c>
+      <c r="P1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1018" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1018" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1018" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="Y1018" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1018" t="n">
+        <v>9.369999999999999</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1019" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>C. CUESTA DE SANTOS</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="G1019" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H1019" t="n">
+        <v>147</v>
+      </c>
+      <c r="I1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1019" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1019" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1019" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z1019" t="n">
+        <v>66.81999999999999</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1020" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>E. BOADA MONTESDEOCA</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="G1020" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H1020" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="I1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1020" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1021" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="G1021" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1021" t="n">
+        <v>240</v>
+      </c>
+      <c r="I1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1021" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1021" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1021" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1021" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="Y1021" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1021" t="n">
+        <v>9.369999999999999</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1022" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>J. VILASANCHEZ FREIJOMIL</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="G1022" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1022" t="n">
+        <v>240</v>
+      </c>
+      <c r="I1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1022" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1022" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1022" t="n">
+        <v>1</v>
+      </c>
+      <c r="O1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1022" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1022" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1022" t="n">
+        <v>47.78</v>
+      </c>
+      <c r="Y1022" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1022" t="n">
+        <v>9.369999999999999</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1023" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>P. DOMINGUEZ LORENZO</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="G1023" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H1023" t="n">
+        <v>199.2</v>
+      </c>
+      <c r="I1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1023" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1023" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1023" t="n">
+        <v>52.1</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1024" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>A. SIMON DEL CORRAL</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="G1024" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H1024" t="n">
+        <v>33</v>
+      </c>
+      <c r="I1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1024" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1025" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>D. FERNANDEZ CAÑAS</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="G1025" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H1025" t="n">
+        <v>172.8</v>
+      </c>
+      <c r="I1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1025" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1025" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1025" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1025" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1025" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1025" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1025" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1025" t="n">
+        <v>-39.57</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1026" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>G. DIAZ MONTERO</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="G1026" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H1026" t="n">
+        <v>207</v>
+      </c>
+      <c r="I1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1026" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1026" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1026" t="n">
+        <v>-11.74</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1027" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>G. LARDIES GUILLEN</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="G1027" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="H1027" t="n">
+        <v>160.2</v>
+      </c>
+      <c r="I1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1027" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1027" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1027" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1027" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="Y1027" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1027" t="n">
+        <v>48.51</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1028" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>H. PEREZ SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="G1028" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H1028" t="n">
+        <v>33</v>
+      </c>
+      <c r="I1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1028" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1029" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>J. ATIENZA PEREA</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="G1029" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1029" t="n">
+        <v>240</v>
+      </c>
+      <c r="I1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1029" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1029" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1029" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1029" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1029" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="Y1029" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1029" t="n">
+        <v>-9.369999999999999</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1030" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>J. DE DOMINGO GARAY</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="G1030" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H1030" t="n">
+        <v>207</v>
+      </c>
+      <c r="I1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1030" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1030" t="n">
+        <v>-11.74</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1031" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>N. MAIGA</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="G1031" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H1031" t="n">
+        <v>147</v>
+      </c>
+      <c r="I1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1031" t="n">
+        <v>2</v>
+      </c>
+      <c r="O1031" t="n">
+        <v>1</v>
+      </c>
+      <c r="P1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1031" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="Y1031" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z1031" t="n">
+        <v>-66.81999999999999</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1032" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>J. AYALA AYLLÓN</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="G1032" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H1032" t="n">
+        <v>288</v>
+      </c>
+      <c r="I1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1032" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1032" t="n">
+        <v>2</v>
+      </c>
+      <c r="O1032" t="n">
+        <v>1</v>
+      </c>
+      <c r="P1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1032" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1032" t="n">
+        <v>2</v>
+      </c>
+      <c r="V1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1032" t="n">
+        <v>2</v>
+      </c>
+      <c r="X1032" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="Y1032" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1032" t="n">
+        <v>-26.18</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1033" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>J. SAEZ BENITO</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="G1033" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="H1033" t="n">
+        <v>223.8</v>
+      </c>
+      <c r="I1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1033" t="n">
+        <v>2</v>
+      </c>
+      <c r="O1033" t="n">
+        <v>1</v>
+      </c>
+      <c r="P1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1033" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1033" t="n">
+        <v>1</v>
+      </c>
+      <c r="U1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1033" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="Y1033" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1033" t="n">
+        <v>-41.22</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1034" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>L. BERMEJO ALCALDE</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="G1034" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H1034" t="n">
+        <v>235.8</v>
+      </c>
+      <c r="I1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1034" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1034" t="n">
+        <v>-9.67</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1035" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>M. ALARCON ORTIZ</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="G1035" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H1035" t="n">
+        <v>166.8</v>
+      </c>
+      <c r="I1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1035" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1035" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1035" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1035" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1035" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="Y1035" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z1035" t="n">
+        <v>41.97</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1036" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>M. BATLLE BERNARDO</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="G1036" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H1036" t="n">
+        <v>288</v>
+      </c>
+      <c r="I1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1036" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1036" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1036" t="n">
+        <v>2</v>
+      </c>
+      <c r="O1036" t="n">
+        <v>2</v>
+      </c>
+      <c r="P1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1036" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="Y1036" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1036" t="n">
+        <v>-26.18</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1037" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>M. DEL VALLE REGALADO</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="G1037" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H1037" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="I1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1037" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1037" t="n">
+        <v>1</v>
+      </c>
+      <c r="U1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1037" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="Y1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1037" t="n">
+        <v>-130.56</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1038" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>S. RODRIGUEZ GREGORIO</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="G1038" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="H1038" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="I1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1038" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1038" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1038" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1038" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1038" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="Y1038" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z1038" t="n">
+        <v>-81.02</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1039" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>D. MANZANERO CAMACHO</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="G1039" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H1039" t="n">
+        <v>288</v>
+      </c>
+      <c r="I1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1039" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1039" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1039" t="n">
+        <v>2</v>
+      </c>
+      <c r="V1039" t="n">
+        <v>2</v>
+      </c>
+      <c r="W1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1039" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="Y1039" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1039" t="n">
+        <v>26.18</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1040" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>J. GARCIA-LARRACHE SEGURA</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="G1040" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H1040" t="n">
+        <v>190.8</v>
+      </c>
+      <c r="I1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1040" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1040" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1040" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1040" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1040" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="Y1040" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z1040" t="n">
+        <v>101.8</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1041" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>J. LAPASTORA ARACIL</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="G1041" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H1041" t="n">
+        <v>235.8</v>
+      </c>
+      <c r="I1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1041" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1041" t="n">
+        <v>2</v>
+      </c>
+      <c r="V1041" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1041" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1041" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="Y1041" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1041" t="n">
+        <v>9.67</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1042" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>L. GARCIA LARRACHE SEGURA</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="G1042" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H1042" t="n">
+        <v>288</v>
+      </c>
+      <c r="I1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1042" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1042" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1042" t="n">
+        <v>3</v>
+      </c>
+      <c r="O1042" t="n">
+        <v>3</v>
+      </c>
+      <c r="P1042" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1042" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="Y1042" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1042" t="n">
+        <v>26.18</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1043" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>M. HERMOSO ALCUBILLA</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="G1043" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H1043" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="I1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1043" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1043" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y1043" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z1043" t="n">
+        <v>-31.97</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1044" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>M. KREISLER LORENTE</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="G1044" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H1044" t="n">
+        <v>139.2</v>
+      </c>
+      <c r="I1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1044" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1044" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1044" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="Y1044" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z1044" t="n">
+        <v>97.41</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1045" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>P. FUENTE DIEZ</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="G1045" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H1045" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="I1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1045" t="n">
+        <v>1</v>
+      </c>
+      <c r="U1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1045" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z1045" t="n">
+        <v>-31.97</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1046" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>A. GASE SECO</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="G1046" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H1046" t="n">
+        <v>292.2</v>
+      </c>
+      <c r="I1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1046" t="n">
+        <v>6</v>
+      </c>
+      <c r="O1046" t="n">
+        <v>2</v>
+      </c>
+      <c r="P1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1046" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1046" t="n">
+        <v>2</v>
+      </c>
+      <c r="V1046" t="n">
+        <v>2</v>
+      </c>
+      <c r="W1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1046" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="Y1046" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z1046" t="n">
+        <v>82.86</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1047" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>G. MEJÍA ACOSTA</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="G1047" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H1047" t="n">
+        <v>292.2</v>
+      </c>
+      <c r="I1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1047" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1047" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1047" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1047" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1047" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="Y1047" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z1047" t="n">
+        <v>82.86</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1048" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="G1048" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H1048" t="n">
+        <v>273</v>
+      </c>
+      <c r="I1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1048" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1048" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1048" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z1048" t="n">
+        <v>86.28</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1049" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>J. ABRIL RAMIRO</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="G1049" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H1049" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="I1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1049" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z1049" t="n">
+        <v>-66.67</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1050" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>J. GONZÁLEZ CHÁVEZ</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="G1050" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="H1050" t="n">
+        <v>202.2</v>
+      </c>
+      <c r="I1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1050" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1050" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1050" t="n">
+        <v>2</v>
+      </c>
+      <c r="S1050" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1050" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1050" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1050" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="Y1050" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z1050" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1051" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>K. SKUTYELNIK</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="G1051" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H1051" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1051" t="n">
+        <v>4</v>
+      </c>
+      <c r="O1051" t="n">
+        <v>4</v>
+      </c>
+      <c r="P1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1051" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1051" t="n">
+        <v>27.27</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1052" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>O. BALSELLS PLAZA</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="G1052" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H1052" t="n">
+        <v>289.2</v>
+      </c>
+      <c r="I1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1052" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1052" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1052" t="n">
+        <v>2</v>
+      </c>
+      <c r="M1052" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1052" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1052" t="n">
+        <v>3</v>
+      </c>
+      <c r="V1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1052" t="n">
+        <v>3</v>
+      </c>
+      <c r="X1052" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="Y1052" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z1052" t="n">
+        <v>72.98</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1053" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>S. GUEYE</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="G1053" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H1053" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="I1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1053" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1053" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1054" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>A. BIERSACK LOPEZ</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="G1054" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="H1054" t="n">
+        <v>259.2</v>
+      </c>
+      <c r="I1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1054" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1054" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1054" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1054" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="Y1054" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Z1054" t="n">
+        <v>-141.84</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1055" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>A. GARCIA QUILEZ CUERVAS</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="G1055" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H1055" t="n">
+        <v>172.8</v>
+      </c>
+      <c r="I1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1055" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1055" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1055" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y1055" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1055" t="n">
+        <v>-21.48</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1056" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>A. PEREZ CONTI</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="G1056" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H1056" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="I1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1056" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1056" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1056" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1056" t="n">
+        <v>4</v>
+      </c>
+      <c r="V1056" t="n">
+        <v>3</v>
+      </c>
+      <c r="W1056" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1056" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="Y1056" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1056" t="n">
+        <v>-20.14</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1057" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>C. CRESPO MONTESINOS</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="G1057" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H1057" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="I1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1057" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1057" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1057" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1057" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y1057" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z1057" t="n">
+        <v>-175.68</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1058" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="G1058" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H1058" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="I1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1058" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z1058" t="n">
+        <v>-215.15</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1059" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>G. MARTIN LOPEZ-LAGO</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="G1059" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H1059" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="I1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1059" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1059" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1059" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1059" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y1059" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z1059" t="n">
+        <v>-139.78</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1060" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>O. HADI ADEGBITE</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="G1060" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H1060" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="I1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1060" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z1060" t="n">
+        <v>-146.1</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1061" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>O. MENDEZ BLANCO</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="G1061" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="H1061" t="n">
+        <v>226.2</v>
+      </c>
+      <c r="I1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1061" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1061" t="n">
+        <v>3</v>
+      </c>
+      <c r="M1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1061" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1061" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y1061" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z1061" t="n">
+        <v>-46.62</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1062" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>P. ESTEBANEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="G1062" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="H1062" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="I1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1062" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1062" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1062" t="n">
+        <v>1</v>
+      </c>
+      <c r="U1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1062" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="Y1062" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1062" t="n">
+        <v>-19.71</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1063" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>A. VICENTE VIANA</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="G1063" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H1063" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="I1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1063" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z1063" t="n">
+        <v>-33.79</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1064" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>B. GUEYE</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="G1064" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H1064" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="I1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1064" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1064" t="n">
+        <v>2</v>
+      </c>
+      <c r="O1064" t="n">
+        <v>1</v>
+      </c>
+      <c r="P1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1064" t="n">
+        <v>40.52</v>
+      </c>
+      <c r="Y1064" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z1064" t="n">
+        <v>-33.79</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1065" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>C. KLOTZ MAROTO</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="G1065" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H1065" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="I1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1065" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1065" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1066" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>C. UNANUE CEGARRA</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="G1066" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H1066" t="n">
+        <v>51</v>
+      </c>
+      <c r="I1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1066" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1066" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1066" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="Y1066" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1066" t="n">
+        <v>70.45</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1067" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>D. LORENZO NEGRETE</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="G1067" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H1067" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="I1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1067" t="n">
+        <v>4</v>
+      </c>
+      <c r="O1067" t="n">
+        <v>3</v>
+      </c>
+      <c r="P1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1067" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1067" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1067" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="Y1067" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z1067" t="n">
+        <v>-33.79</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1068" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>S. GACIC</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="G1068" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H1068" t="n">
+        <v>79.80000000000001</v>
+      </c>
+      <c r="I1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1068" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1068" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="Y1068" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z1068" t="n">
+        <v>-98.61</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1069" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>V. ALONSO PASCUAL</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="G1069" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H1069" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="I1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1069" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1069" t="n">
+        <v>-146.81</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1070" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="G1070" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H1070" t="n">
+        <v>129</v>
+      </c>
+      <c r="I1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1070" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1070" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1070" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1070" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1070" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y1070" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z1070" t="n">
+        <v>79.08</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1071" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>B. FERNANDEZ SHEPHARD</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="G1071" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H1071" t="n">
+        <v>39</v>
+      </c>
+      <c r="I1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1071" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1071" t="n">
+        <v>146.81</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1072" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>J. GALLETTO LAMELA</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="G1072" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H1072" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="I1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1072" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1072" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1072" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1072" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1072" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y1072" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z1072" t="n">
+        <v>33.79</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1073" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>K. RIVEROL DE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="G1073" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H1073" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="I1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1073" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z1073" t="n">
+        <v>33.79</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1074" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>M. NIMAGA</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="G1074" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H1074" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="I1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1074" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1074" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1074" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1074" t="n">
+        <v>2</v>
+      </c>
+      <c r="V1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1074" t="n">
+        <v>2</v>
+      </c>
+      <c r="X1074" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y1074" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1074" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1075" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="G1075" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H1075" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1075" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="C1076" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>S. MANERO GUZMAN</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="G1076" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H1076" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="I1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1076" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z1076" t="n">
+        <v>33.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
